--- a/RAMON FRANCO/Agosto/CALCULO EDESUR RAMON FRANCO Agosto.xlsx
+++ b/RAMON FRANCO/Agosto/CALCULO EDESUR RAMON FRANCO Agosto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AA20A2-C12E-4553-87F7-C625865B8F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CC8ACB-95C9-4511-94CE-2ED98BD4CFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -339,7 +339,7 @@
     <t>QUIENES ADEUDEN DOS MESES DE EDESUR SERAN DESCONECTADOS DE LA RED. SALUDOS CORDIALES.</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 14/08</t>
+    <t>EDESUR - VENCIMIENTO 15/09</t>
   </si>
 </sst>
 </file>
@@ -355,7 +355,7 @@
     <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,12 +430,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,19 +438,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,12 +484,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,7 +754,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -862,7 +844,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -886,12 +867,6 @@
     <xf numFmtId="165" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="8" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -905,7 +880,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="7" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="8" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -917,6 +891,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -926,27 +901,29 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="8" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1255,11 +1232,12 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" customWidth="1"/>
     <col min="6" max="7" width="10.85546875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.42578125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="13" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="7.140625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="9.85546875" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="15.42578125" customWidth="1"/>
@@ -1272,22 +1250,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="91"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="88"/>
       <c r="O1" s="48"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3"/>
@@ -1440,18 +1418,18 @@
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="95">
-        <v>649906.67000000004</v>
+      <c r="C8" s="84">
+        <v>1297943.02</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="47">
+      <c r="J8" s="92"/>
+      <c r="K8" s="93">
         <f>C8-J32</f>
-        <v>319359.07784999989</v>
+        <v>872391.07259</v>
       </c>
       <c r="L8" s="47"/>
       <c r="M8" s="10"/>
@@ -1484,13 +1462,13 @@
       <c r="H9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="40" t="s">
+      <c r="J9" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="44" t="s">
+      <c r="K9" s="96" t="s">
         <v>94</v>
       </c>
       <c r="L9" s="44" t="s">
@@ -1504,75 +1482,76 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="60">
+      <c r="A10" s="59">
         <v>1</v>
       </c>
-      <c r="B10" s="96">
+      <c r="B10" s="101">
         <v>1</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="C10" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="99">
+      <c r="E10" s="73">
         <v>7.99</v>
       </c>
-      <c r="F10" s="100">
-        <v>5305</v>
-      </c>
-      <c r="G10" s="101">
+      <c r="F10" s="102">
+        <f>+E10</f>
+        <v>7.99</v>
+      </c>
+      <c r="G10" s="102">
         <f>+F10</f>
-        <v>5305</v>
-      </c>
-      <c r="H10" s="102">
-        <v>0</v>
-      </c>
-      <c r="I10" s="103">
+        <v>7.99</v>
+      </c>
+      <c r="H10" s="74">
+        <v>0</v>
+      </c>
+      <c r="I10" s="75">
         <f t="shared" ref="I10:I32" si="0">H10*7%</f>
         <v>0</v>
       </c>
-      <c r="J10" s="104">
+      <c r="J10" s="99">
         <f>M10*93.787</f>
         <v>0</v>
       </c>
-      <c r="K10" s="105">
+      <c r="K10" s="99">
         <f>K8*E10%</f>
-        <v>25516.79032021499</v>
-      </c>
-      <c r="L10" s="105"/>
-      <c r="M10" s="106">
+        <v>69704.046699940998</v>
+      </c>
+      <c r="L10" s="76"/>
+      <c r="M10" s="77">
         <f>G10-F10</f>
         <v>0</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="78">
         <f>J10+K10+L10</f>
-        <v>25516.79032021499</v>
+        <v>69704.046699940998</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="60">
+      <c r="A11" s="59">
         <v>2</v>
       </c>
-      <c r="B11" s="59">
+      <c r="B11" s="58">
         <v>2</v>
       </c>
       <c r="C11" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="87" t="s">
+      <c r="D11" s="83" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="53">
         <v>6.05</v>
       </c>
-      <c r="F11" s="60">
-        <v>6943</v>
-      </c>
-      <c r="G11" s="94">
-        <f>F11+200</f>
-        <v>7143</v>
+      <c r="F11" s="100">
+        <f>E11+200</f>
+        <v>206.05</v>
+      </c>
+      <c r="G11" s="100">
+        <v>490.1</v>
       </c>
       <c r="H11" s="54">
         <v>0</v>
@@ -1581,29 +1560,29 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="56">
+      <c r="J11" s="97">
         <f t="shared" ref="J11:J27" si="1">M11*93.787</f>
-        <v>18757.400000000001</v>
-      </c>
-      <c r="K11" s="57">
+        <v>26640.197350000002</v>
+      </c>
+      <c r="K11" s="97">
         <f>K8*E11%</f>
-        <v>19321.224209924992</v>
-      </c>
-      <c r="L11" s="57"/>
-      <c r="M11" s="58">
+        <v>52779.659891694995</v>
+      </c>
+      <c r="L11" s="56"/>
+      <c r="M11" s="57">
         <f t="shared" ref="M11:M31" si="2">G11-F11</f>
-        <v>200</v>
-      </c>
-      <c r="N11" s="72">
+        <v>284.05</v>
+      </c>
+      <c r="N11" s="69">
         <f t="shared" ref="N11:N31" si="3">J11+K11+L11</f>
-        <v>38078.624209924994</v>
+        <v>79419.85724169499</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="60">
+      <c r="A12" s="59">
         <v>3</v>
       </c>
-      <c r="B12" s="59">
+      <c r="B12" s="58">
         <v>3</v>
       </c>
       <c r="C12" s="51" t="s">
@@ -1615,11 +1594,11 @@
       <c r="E12" s="53">
         <v>6.02</v>
       </c>
-      <c r="F12" s="60">
-        <v>4133.7</v>
-      </c>
-      <c r="G12" s="94">
+      <c r="F12" s="100">
         <v>4519.8999999999996</v>
+      </c>
+      <c r="G12" s="100">
+        <v>4880.8999999999996</v>
       </c>
       <c r="H12" s="54">
         <v>0</v>
@@ -1628,77 +1607,78 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="56">
+      <c r="J12" s="97">
         <f t="shared" si="1"/>
-        <v>36220.539399999987</v>
-      </c>
-      <c r="K12" s="57">
+        <v>33857.107000000004</v>
+      </c>
+      <c r="K12" s="97">
         <f>K8*E12%</f>
-        <v>19225.416486569993</v>
-      </c>
-      <c r="L12" s="57"/>
-      <c r="M12" s="58">
+        <v>52517.942569917999</v>
+      </c>
+      <c r="L12" s="56"/>
+      <c r="M12" s="57">
         <f>G12-F12</f>
-        <v>386.19999999999982</v>
-      </c>
-      <c r="N12" s="72">
+        <v>361</v>
+      </c>
+      <c r="N12" s="69">
         <f t="shared" si="3"/>
-        <v>55445.95588656998</v>
+        <v>86375.049569918003</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="60">
+      <c r="A13" s="59">
         <v>4</v>
       </c>
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="64" t="s">
+      <c r="D13" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E13" s="64">
         <v>7.63</v>
       </c>
-      <c r="F13" s="60">
-        <v>3010</v>
-      </c>
-      <c r="G13" s="94">
+      <c r="F13" s="100">
+        <f>E13+250</f>
+        <v>257.63</v>
+      </c>
+      <c r="G13" s="100">
         <f>F13+250</f>
-        <v>3260</v>
-      </c>
-      <c r="H13" s="66">
-        <v>0</v>
-      </c>
-      <c r="I13" s="67">
+        <v>507.63</v>
+      </c>
+      <c r="H13" s="65">
+        <v>0</v>
+      </c>
+      <c r="I13" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="56">
+      <c r="J13" s="97">
         <f t="shared" si="1"/>
         <v>23446.75</v>
       </c>
-      <c r="K13" s="68">
+      <c r="K13" s="98">
         <f>K8*E13%</f>
-        <v>24367.097639954987</v>
-      </c>
-      <c r="L13" s="57"/>
-      <c r="M13" s="69">
+        <v>66563.438838616989</v>
+      </c>
+      <c r="L13" s="56"/>
+      <c r="M13" s="66">
         <f t="shared" si="2"/>
         <v>250</v>
       </c>
-      <c r="N13" s="72">
+      <c r="N13" s="69">
         <f t="shared" si="3"/>
-        <v>47813.847639954984</v>
+        <v>90010.188838616989</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="60">
+      <c r="A14" s="59">
         <v>6</v>
       </c>
-      <c r="B14" s="59">
+      <c r="B14" s="58">
         <v>6</v>
       </c>
       <c r="C14" s="51" t="s">
@@ -1710,12 +1690,13 @@
       <c r="E14" s="53">
         <v>6.05</v>
       </c>
-      <c r="F14" s="60">
-        <v>15363</v>
-      </c>
-      <c r="G14" s="94">
+      <c r="F14" s="100">
+        <f>+E14+250</f>
+        <v>256.05</v>
+      </c>
+      <c r="G14" s="100">
         <f>+F14+250</f>
-        <v>15613</v>
+        <v>506.05</v>
       </c>
       <c r="H14" s="54">
         <v>0</v>
@@ -1724,29 +1705,29 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="56">
+      <c r="J14" s="97">
         <f t="shared" si="1"/>
         <v>23446.75</v>
       </c>
-      <c r="K14" s="57">
+      <c r="K14" s="97">
         <f>K8*E14%</f>
-        <v>19321.224209924992</v>
-      </c>
-      <c r="L14" s="57"/>
-      <c r="M14" s="58">
+        <v>52779.659891694995</v>
+      </c>
+      <c r="L14" s="56"/>
+      <c r="M14" s="57">
         <f t="shared" si="2"/>
         <v>250</v>
       </c>
-      <c r="N14" s="72">
+      <c r="N14" s="69">
         <f>J14+K14+L14</f>
-        <v>42767.974209924992</v>
+        <v>76226.409891694988</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="60">
+      <c r="A15" s="59">
         <v>7</v>
       </c>
-      <c r="B15" s="59">
+      <c r="B15" s="58">
         <v>7</v>
       </c>
       <c r="C15" s="51" t="s">
@@ -1758,11 +1739,11 @@
       <c r="E15" s="53">
         <v>6.02</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="100">
         <v>4914.8999999999996</v>
       </c>
-      <c r="G15" s="94">
-        <v>4914.8999999999996</v>
+      <c r="G15" s="100">
+        <v>5019.8</v>
       </c>
       <c r="H15" s="54">
         <v>0</v>
@@ -1771,29 +1752,29 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="56">
+      <c r="J15" s="97">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="57">
+        <v>9838.2563000000519</v>
+      </c>
+      <c r="K15" s="97">
         <f>K8*E15%</f>
-        <v>19225.416486569993</v>
-      </c>
-      <c r="L15" s="57"/>
-      <c r="M15" s="58">
+        <v>52517.942569917999</v>
+      </c>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="72">
+        <v>104.90000000000055</v>
+      </c>
+      <c r="N15" s="69">
         <f t="shared" si="3"/>
-        <v>19225.416486569993</v>
+        <v>62356.198869918051</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="60">
+      <c r="A16" s="59">
         <v>8</v>
       </c>
-      <c r="B16" s="59">
+      <c r="B16" s="58">
         <v>8</v>
       </c>
       <c r="C16" s="51" t="s">
@@ -1805,11 +1786,11 @@
       <c r="E16" s="53">
         <v>7.63</v>
       </c>
-      <c r="F16" s="60">
-        <v>14006.5</v>
-      </c>
-      <c r="G16" s="94">
+      <c r="F16" s="100">
         <v>14488.2</v>
+      </c>
+      <c r="G16" s="100">
+        <v>14922.1</v>
       </c>
       <c r="H16" s="26">
         <v>0</v>
@@ -1818,30 +1799,30 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="56">
+      <c r="J16" s="97">
         <f t="shared" si="1"/>
-        <v>45177.197900000072</v>
-      </c>
-      <c r="K16" s="57">
+        <v>40694.179299999967</v>
+      </c>
+      <c r="K16" s="97">
         <f>K8*E16%</f>
-        <v>24367.097639954987</v>
-      </c>
-      <c r="L16" s="57"/>
-      <c r="M16" s="58">
+        <v>66563.438838616989</v>
+      </c>
+      <c r="L16" s="56"/>
+      <c r="M16" s="57">
         <f t="shared" si="2"/>
-        <v>481.70000000000073</v>
-      </c>
-      <c r="N16" s="72">
+        <v>433.89999999999964</v>
+      </c>
+      <c r="N16" s="69">
         <f t="shared" si="3"/>
-        <v>69544.295539955056</v>
+        <v>107257.61813861696</v>
       </c>
       <c r="P16" s="50"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="60">
+      <c r="A17" s="59">
         <v>9</v>
       </c>
-      <c r="B17" s="59">
+      <c r="B17" s="58">
         <v>9</v>
       </c>
       <c r="C17" s="51" t="s">
@@ -1853,11 +1834,11 @@
       <c r="E17" s="53">
         <v>6.05</v>
       </c>
-      <c r="F17" s="60">
-        <v>10481.540000000001</v>
-      </c>
-      <c r="G17" s="94">
+      <c r="F17" s="100">
         <v>10498.59</v>
+      </c>
+      <c r="G17" s="100">
+        <v>10499.21</v>
       </c>
       <c r="H17" s="54">
         <v>0</v>
@@ -1866,29 +1847,29 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="56">
+      <c r="J17" s="97">
         <f t="shared" si="1"/>
-        <v>1599.0683499999318</v>
-      </c>
-      <c r="K17" s="57">
+        <v>58.147939999904466</v>
+      </c>
+      <c r="K17" s="97">
         <f>K8*E17%</f>
-        <v>19321.224209924992</v>
-      </c>
-      <c r="L17" s="57"/>
-      <c r="M17" s="58">
+        <v>52779.659891694995</v>
+      </c>
+      <c r="L17" s="56"/>
+      <c r="M17" s="57">
         <f t="shared" si="2"/>
-        <v>17.049999999999272</v>
-      </c>
-      <c r="N17" s="72">
+        <v>0.61999999999898137</v>
+      </c>
+      <c r="N17" s="69">
         <f t="shared" si="3"/>
-        <v>20920.292559924925</v>
+        <v>52837.807831694903</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="60">
+      <c r="A18" s="59">
         <v>10</v>
       </c>
-      <c r="B18" s="59">
+      <c r="B18" s="58">
         <v>10</v>
       </c>
       <c r="C18" s="51" t="s">
@@ -1900,11 +1881,11 @@
       <c r="E18" s="53">
         <v>6.02</v>
       </c>
-      <c r="F18" s="60">
-        <v>8123.2</v>
-      </c>
-      <c r="G18" s="94">
+      <c r="F18" s="100">
         <v>8344.6</v>
+      </c>
+      <c r="G18" s="100">
+        <v>8492.7999999999993</v>
       </c>
       <c r="H18" s="54">
         <v>0</v>
@@ -1913,45 +1894,45 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="56">
+      <c r="J18" s="97">
         <f t="shared" si="1"/>
-        <v>20764.441800000051</v>
-      </c>
-      <c r="K18" s="57">
+        <v>13899.233399999899</v>
+      </c>
+      <c r="K18" s="97">
         <f>K8*E18%</f>
-        <v>19225.416486569993</v>
-      </c>
-      <c r="L18" s="57"/>
-      <c r="M18" s="58">
+        <v>52517.942569917999</v>
+      </c>
+      <c r="L18" s="56"/>
+      <c r="M18" s="57">
         <f t="shared" si="2"/>
-        <v>221.40000000000055</v>
-      </c>
-      <c r="N18" s="72">
+        <v>148.19999999999891</v>
+      </c>
+      <c r="N18" s="69">
         <f t="shared" si="3"/>
-        <v>39989.858286570045</v>
+        <v>66417.175969917895</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="60">
+      <c r="A19" s="59">
         <v>11</v>
       </c>
-      <c r="B19" s="59">
+      <c r="B19" s="58">
         <v>11</v>
       </c>
       <c r="C19" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="D19" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="70">
+      <c r="E19" s="67">
         <v>21.2</v>
       </c>
-      <c r="F19" s="60">
-        <v>22160.44</v>
-      </c>
-      <c r="G19" s="94">
+      <c r="F19" s="100">
         <v>22661.67</v>
+      </c>
+      <c r="G19" s="100">
+        <v>23124.77</v>
       </c>
       <c r="H19" s="26">
         <v>0</v>
@@ -1960,46 +1941,47 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="56">
+      <c r="J19" s="97">
         <f t="shared" si="1"/>
-        <v>47008.85800999996</v>
-      </c>
-      <c r="K19" s="57">
+        <v>43432.759700000206</v>
+      </c>
+      <c r="K19" s="97">
         <f>K8*E19%</f>
-        <v>67704.124504199979</v>
-      </c>
-      <c r="L19" s="57"/>
-      <c r="M19" s="58">
+        <v>184946.90738908001</v>
+      </c>
+      <c r="L19" s="56"/>
+      <c r="M19" s="57">
         <f>G19-F19</f>
-        <v>501.22999999999956</v>
-      </c>
-      <c r="N19" s="72">
+        <v>463.10000000000218</v>
+      </c>
+      <c r="N19" s="69">
         <f t="shared" si="3"/>
-        <v>114712.98251419995</v>
+        <v>228379.66708908021</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="60">
+      <c r="A20" s="59">
         <v>12</v>
       </c>
-      <c r="B20" s="59">
+      <c r="B20" s="58">
         <v>12</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="60" t="s">
         <v>70</v>
       </c>
       <c r="E20" s="53">
         <v>6.81</v>
       </c>
-      <c r="F20" s="60">
-        <v>7840</v>
-      </c>
-      <c r="G20" s="94">
-        <f>F20+480</f>
-        <v>8320</v>
+      <c r="F20" s="100">
+        <f>E20+480</f>
+        <v>486.81</v>
+      </c>
+      <c r="G20" s="100">
+        <f>F20+600</f>
+        <v>1086.81</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
@@ -2008,30 +1990,30 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="56">
+      <c r="J20" s="97">
         <f t="shared" si="1"/>
-        <v>45017.760000000002</v>
-      </c>
-      <c r="K20" s="57">
+        <v>56272.200000000004</v>
+      </c>
+      <c r="K20" s="97">
         <f>K8*E20%</f>
-        <v>21748.353201584989</v>
-      </c>
-      <c r="L20" s="57"/>
-      <c r="M20" s="58">
+        <v>59409.832043378992</v>
+      </c>
+      <c r="L20" s="56"/>
+      <c r="M20" s="57">
         <f t="shared" si="2"/>
-        <v>480</v>
-      </c>
-      <c r="N20" s="72">
+        <v>600</v>
+      </c>
+      <c r="N20" s="69">
         <f t="shared" si="3"/>
-        <v>66766.113201584987</v>
+        <v>115682.032043379</v>
       </c>
       <c r="P20" s="33"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="60">
+      <c r="A21" s="59">
         <v>13</v>
       </c>
-      <c r="B21" s="59">
+      <c r="B21" s="58">
         <v>13</v>
       </c>
       <c r="C21" s="51" t="s">
@@ -2043,11 +2025,11 @@
       <c r="E21" s="53">
         <v>6.52</v>
       </c>
-      <c r="F21" s="60">
-        <v>12529.4</v>
-      </c>
-      <c r="G21" s="94">
+      <c r="F21" s="100">
         <v>13266.27</v>
+      </c>
+      <c r="G21" s="100">
+        <v>14907.93</v>
       </c>
       <c r="H21" s="26">
         <v>0</v>
@@ -2056,123 +2038,123 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="56">
+      <c r="J21" s="97">
         <f t="shared" si="1"/>
-        <v>69108.826690000074</v>
-      </c>
-      <c r="K21" s="57">
+        <v>153966.36642000001</v>
+      </c>
+      <c r="K21" s="97">
         <f>K8*E21%</f>
-        <v>20822.21187581999</v>
-      </c>
-      <c r="L21" s="57"/>
-      <c r="M21" s="58">
+        <v>56879.897932867992</v>
+      </c>
+      <c r="L21" s="56"/>
+      <c r="M21" s="57">
         <f t="shared" si="2"/>
-        <v>736.8700000000008</v>
-      </c>
-      <c r="N21" s="72">
+        <v>1641.6599999999999</v>
+      </c>
+      <c r="N21" s="69">
         <f t="shared" si="3"/>
-        <v>89931.038565820068</v>
+        <v>210846.26435286799</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>14</v>
       </c>
-      <c r="B22" s="83">
+      <c r="B22" s="79">
         <v>14</v>
       </c>
-      <c r="C22" s="74" t="s">
+      <c r="C22" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="75" t="s">
+      <c r="D22" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="76">
+      <c r="E22" s="73">
         <v>1.18</v>
       </c>
-      <c r="F22" s="84">
-        <v>0</v>
-      </c>
-      <c r="G22" s="84">
-        <v>0</v>
-      </c>
-      <c r="H22" s="77">
-        <v>0</v>
-      </c>
-      <c r="I22" s="78">
+      <c r="F22" s="80">
+        <v>0</v>
+      </c>
+      <c r="G22" s="80">
+        <v>0</v>
+      </c>
+      <c r="H22" s="74">
+        <v>0</v>
+      </c>
+      <c r="I22" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="79">
+      <c r="J22" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="80">
+      <c r="K22" s="99">
         <f>K8*E22%</f>
-        <v>3768.4371186299986</v>
-      </c>
-      <c r="L22" s="80"/>
-      <c r="M22" s="81">
+        <v>10294.214656562001</v>
+      </c>
+      <c r="L22" s="76"/>
+      <c r="M22" s="77">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N22" s="82">
+      <c r="N22" s="78">
         <f t="shared" si="3"/>
-        <v>3768.4371186299986</v>
+        <v>10294.214656562001</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>15</v>
       </c>
-      <c r="B23" s="83">
+      <c r="B23" s="79">
         <v>15</v>
       </c>
-      <c r="C23" s="74" t="s">
+      <c r="C23" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="75" t="s">
+      <c r="D23" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="76">
+      <c r="E23" s="73">
         <v>1.17</v>
       </c>
-      <c r="F23" s="84">
-        <v>0</v>
-      </c>
-      <c r="G23" s="84">
-        <v>0</v>
-      </c>
-      <c r="H23" s="77">
-        <v>0</v>
-      </c>
-      <c r="I23" s="78">
+      <c r="F23" s="80">
+        <v>0</v>
+      </c>
+      <c r="G23" s="80">
+        <v>0</v>
+      </c>
+      <c r="H23" s="74">
+        <v>0</v>
+      </c>
+      <c r="I23" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="79">
+      <c r="J23" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="80">
+      <c r="K23" s="99">
         <f>K8*E23%</f>
-        <v>3736.5012108449982</v>
-      </c>
-      <c r="L23" s="80"/>
-      <c r="M23" s="81">
+        <v>10206.975549302999</v>
+      </c>
+      <c r="L23" s="76"/>
+      <c r="M23" s="77">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N23" s="82">
+      <c r="N23" s="78">
         <f t="shared" si="3"/>
-        <v>3736.5012108449982</v>
+        <v>10206.975549302999</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
         <v>16</v>
       </c>
-      <c r="B24" s="59">
+      <c r="B24" s="58">
         <v>16</v>
       </c>
       <c r="C24" s="51" t="s">
@@ -2184,10 +2166,10 @@
       <c r="E24" s="53">
         <v>1.06</v>
       </c>
-      <c r="F24" s="60">
-        <v>0</v>
-      </c>
-      <c r="G24" s="60">
+      <c r="F24" s="59">
+        <v>0</v>
+      </c>
+      <c r="G24" s="59">
         <v>0</v>
       </c>
       <c r="H24" s="54">
@@ -2197,69 +2179,69 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="56">
+      <c r="J24" s="97">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="57">
+      <c r="K24" s="97">
         <f>K8*E24%</f>
-        <v>3385.2062252099986</v>
-      </c>
-      <c r="L24" s="57"/>
-      <c r="M24" s="58">
+        <v>9247.3453694540003</v>
+      </c>
+      <c r="L24" s="56"/>
+      <c r="M24" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N24" s="72">
+      <c r="N24" s="69">
         <f t="shared" si="3"/>
-        <v>3385.2062252099986</v>
+        <v>9247.3453694540003</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>17</v>
       </c>
-      <c r="B25" s="83">
+      <c r="B25" s="79">
         <v>17</v>
       </c>
-      <c r="C25" s="74" t="s">
+      <c r="C25" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="85" t="s">
+      <c r="D25" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="76">
+      <c r="E25" s="73">
         <v>0.51</v>
       </c>
-      <c r="F25" s="84">
-        <v>0</v>
-      </c>
-      <c r="G25" s="84">
-        <v>0</v>
-      </c>
-      <c r="H25" s="77">
-        <v>0</v>
-      </c>
-      <c r="I25" s="78">
+      <c r="F25" s="80">
+        <v>0</v>
+      </c>
+      <c r="G25" s="80">
+        <v>0</v>
+      </c>
+      <c r="H25" s="74">
+        <v>0</v>
+      </c>
+      <c r="I25" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="79">
+      <c r="J25" s="99">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="80">
+      <c r="K25" s="99">
         <f>K8*E25%</f>
-        <v>1628.7312970349994</v>
-      </c>
-      <c r="L25" s="80"/>
-      <c r="M25" s="86">
+        <v>4449.1944702090004</v>
+      </c>
+      <c r="L25" s="76"/>
+      <c r="M25" s="82">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N25" s="82">
+      <c r="N25" s="78">
         <f t="shared" si="3"/>
-        <v>1628.7312970349994</v>
+        <v>4449.1944702090004</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2272,7 +2254,7 @@
       <c r="C26" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="68" t="s">
         <v>75</v>
       </c>
       <c r="E26" s="37">
@@ -2291,22 +2273,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="41">
+      <c r="J26" s="94">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="45">
+      <c r="K26" s="95">
         <f>K8*E26%</f>
-        <v>862.26951019499973</v>
+        <v>2355.455895993</v>
       </c>
       <c r="L26" s="45"/>
       <c r="M26" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N26" s="73">
+      <c r="N26" s="70">
         <f t="shared" si="3"/>
-        <v>862.26951019499973</v>
+        <v>2355.455895993</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2344,16 +2326,16 @@
       </c>
       <c r="K27" s="45">
         <f>K8*E27%</f>
-        <v>5812.3352168699985</v>
+        <v>15877.517521138001</v>
       </c>
       <c r="L27" s="45"/>
       <c r="M27" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N27" s="73">
+      <c r="N27" s="70">
         <f t="shared" si="3"/>
-        <v>5812.3352168699985</v>
+        <v>15877.517521138001</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2514,7 +2496,7 @@
       </c>
       <c r="G32" s="18">
         <f>SUM(G14:G31)+G13+G12+G11+G10</f>
-        <v>118335.12999999999</v>
+        <v>84446.090000000011</v>
       </c>
       <c r="H32" s="19">
         <v>0</v>
@@ -2525,11 +2507,11 @@
       </c>
       <c r="J32" s="41">
         <f>J27+J26+J25+J24+J23+J22+J21+J20+J19+J18+J17+J16+J15+J14+J13+J12+J11+J10</f>
-        <v>330547.59215000016</v>
+        <v>425551.94741000002</v>
       </c>
       <c r="K32" s="45">
         <f>K27+K26+K25+K24+K23+K22+K21+K20+K18+K19+K17+K16+K15+K14+K13+K12+K11+K10</f>
-        <v>319359.07784999989</v>
+        <v>872391.07259</v>
       </c>
       <c r="L32" s="45">
         <f>SUM(L10:L31)</f>
@@ -2537,11 +2519,11 @@
       </c>
       <c r="M32" s="43">
         <f>SUM(M14:M31)+M12+M13+M11+M10</f>
-        <v>3524.4500000000007</v>
+        <v>4537.43</v>
       </c>
       <c r="N32" s="19">
         <f>N27+N26+N25+N24+N23+N22+N21+N20+N19+N18+N17+N16+N15+N14+N13++N12+N11+N10</f>
-        <v>649906.66999999993</v>
+        <v>1297943.02</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2561,7 +2543,7 @@
       </c>
       <c r="J33" s="30">
         <f>SUM(J10:J32)</f>
-        <v>661095.18430000031</v>
+        <v>851103.89482000005</v>
       </c>
       <c r="K33" s="46"/>
       <c r="L33" s="46"/>
@@ -2571,7 +2553,7 @@
       </c>
       <c r="N33" s="29">
         <f>SUM(N10:N32)</f>
-        <v>1299813.3399999999</v>
+        <v>2595886.04</v>
       </c>
       <c r="O33" s="5"/>
       <c r="P33" s="2" t="e">
@@ -2583,20 +2565,20 @@
       <c r="A34" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="92" t="s">
+      <c r="C34" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="89"/>
-      <c r="K34" s="90"/>
-      <c r="L34" s="90"/>
-      <c r="M34" s="89"/>
-      <c r="N34" s="90"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="86"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="86"/>
+      <c r="N34" s="87"/>
       <c r="O34" s="31"/>
       <c r="P34" s="2" t="e">
         <f t="shared" si="4"/>
@@ -2612,61 +2594,61 @@
       <c r="P35" s="2"/>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="93" t="s">
+      <c r="C36" s="90" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="93"/>
-      <c r="E36" s="93"/>
-      <c r="F36" s="93"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="93"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="90"/>
+      <c r="I36" s="90"/>
+      <c r="J36" s="90"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="90"/>
       <c r="P36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="93"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="93"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="90"/>
+      <c r="I37" s="90"/>
+      <c r="J37" s="90"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="90"/>
+      <c r="M37" s="90"/>
       <c r="P37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="93"/>
-      <c r="D38" s="93"/>
-      <c r="E38" s="93"/>
-      <c r="F38" s="93"/>
-      <c r="G38" s="93"/>
-      <c r="H38" s="93"/>
-      <c r="I38" s="93"/>
-      <c r="J38" s="93"/>
-      <c r="K38" s="93"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="93"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="90"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="90"/>
+      <c r="H38" s="90"/>
+      <c r="I38" s="90"/>
+      <c r="J38" s="90"/>
+      <c r="K38" s="90"/>
+      <c r="L38" s="90"/>
+      <c r="M38" s="90"/>
       <c r="P38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="93"/>
-      <c r="D39" s="93"/>
-      <c r="E39" s="93"/>
-      <c r="F39" s="93"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="93"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="93"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="90"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="90"/>
+      <c r="I39" s="90"/>
+      <c r="J39" s="90"/>
+      <c r="K39" s="90"/>
+      <c r="L39" s="90"/>
+      <c r="M39" s="90"/>
       <c r="P39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6546,21 +6528,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="91"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="88"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8152,19 +8134,19 @@
       <c r="A35" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="92" t="s">
+      <c r="C35" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
-      <c r="J35" s="89"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="89"/>
-      <c r="M35" s="90"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="86"/>
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="86"/>
+      <c r="L35" s="86"/>
+      <c r="M35" s="87"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
